--- a/converted/tozalangan/chinobod/Sentabr 10 kunlik/Elektr Murojaatlar.xlsx
+++ b/converted/tozalangan/chinobod/Sentabr 10 kunlik/Elektr Murojaatlar.xlsx
@@ -11,11 +11,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>Murojaatlar Sentabr (1–10) Holatiga Ko'ra</t>
   </si>
   <si>
+    <t>Podstansiya</t>
+  </si>
+  <si>
+    <t>Fider</t>
+  </si>
+  <si>
     <t>TP Nomi</t>
   </si>
   <si>
@@ -49,9 +55,18 @@
     <t>Ma'sul xodim (manba)</t>
   </si>
   <si>
+    <t>Eslatma</t>
+  </si>
+  <si>
     <t>Manba (fayl, qator)</t>
   </si>
   <si>
+    <t>Qo'shtepasaroy</t>
+  </si>
+  <si>
+    <t>Sirmoq</t>
+  </si>
+  <si>
     <t>49</t>
   </si>
   <si>
@@ -85,6 +100,9 @@
     <t>chinobod/Elektr Murojaatlar.xlsx [Sentabr], 3-qator</t>
   </si>
   <si>
+    <t>Yangiqishloq</t>
+  </si>
+  <si>
     <t>56</t>
   </si>
   <si>
@@ -106,6 +124,12 @@
     <t>chinobod/Elektr Murojaatlar.xlsx [Sentabr], 4-qator</t>
   </si>
   <si>
+    <t>Paxtakor</t>
+  </si>
+  <si>
+    <t>O'zbekiston</t>
+  </si>
+  <si>
     <t>293189</t>
   </si>
   <si>
@@ -119,6 +143,9 @@
   </si>
   <si>
     <t>Оқтепа</t>
+  </si>
+  <si>
+    <t>TP 177 (Paxtakor / O'zbekiston) Transformatorlar faylida yo'q - TP bog'lanmaydi</t>
   </si>
   <si>
     <t>chinobod/Elektr Murojaatlar.xlsx [Sentabr], 5-qator</t>
@@ -539,17 +566,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="14" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="7" width="22" customWidth="1"/>
-    <col min="8" max="12" width="26" customWidth="1"/>
+    <col min="1" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="9" width="22" customWidth="1"/>
+    <col min="10" max="15" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -564,8 +591,11 @@
       <c r="J1"/>
       <c r="K1"/>
       <c r="L1"/>
+      <c r="M1"/>
+      <c r="N1"/>
+      <c r="O1"/>
     </row>
-    <row r="2" ht="45" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" ht="45" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -587,10 +617,10 @@
       <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J2" s="4" t="s">
@@ -602,121 +632,151 @@
       <c r="L2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="M2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1">
         <v>46269</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46272</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="L3" t="s">
+      <c r="I4" t="s">
         <v>23</v>
       </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46273</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="1">
-        <v>46272</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="M5" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="1">
-        <v>46273</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" t="s">
-        <v>36</v>
+      <c r="N5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O5" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
